--- a/Packages/cn.etetet.twsmap/Luban/Config/Base/__tables__.xlsx
+++ b/Packages/cn.etetet.twsmap/Luban/Config/Base/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="36">
   <si>
     <t>##var</t>
   </si>
@@ -132,6 +132,9 @@
   </si>
   <si>
     <t>GameLevel</t>
+  </si>
+  <si>
+    <t>EnergyBlock</t>
   </si>
 </sst>
 </file>
@@ -1076,8 +1079,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultColWidth="16.5" defaultRowHeight="14.25" outlineLevelRow="5"/>
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultColWidth="16.5" defaultRowHeight="14.25" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="19.5" customWidth="1"/>
     <col min="2" max="3" width="29.375" customWidth="1"/>
@@ -1206,18 +1209,18 @@
         <v>cn.etetet.yiuilubangen.DemoConfigCategory</v>
       </c>
       <c r="E4" t="str">
-        <f t="shared" ref="E4:E6" si="0">_xlfn.CONCAT(C4,"Config")</f>
+        <f t="shared" ref="E4:E7" si="0">_xlfn.CONCAT(C4,"Config")</f>
         <v>DemoConfig</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
       </c>
       <c r="G4" t="str">
-        <f t="shared" ref="G4:G6" si="1">_xlfn.CONCAT("..\..\..\..\cn.etetet.",B4,"\Luban\Config\Datas\",C4,".xlsx")</f>
+        <f t="shared" ref="G4:G7" si="1">_xlfn.CONCAT("..\..\..\..\cn.etetet.",B4,"\Luban\Config\Datas\",C4,".xlsx")</f>
         <v>..\..\..\..\cn.etetet.yiuilubangen\Luban\Config\Datas\Demo.xlsx</v>
       </c>
       <c r="M4" t="str">
-        <f t="shared" ref="M4:M6" si="2">_xlfn.CONCAT(C4,"ConfigCategory")</f>
+        <f t="shared" ref="M4:M7" si="2">_xlfn.CONCAT(C4,"ConfigCategory")</f>
         <v>DemoConfigCategory</v>
       </c>
     </row>
@@ -1229,7 +1232,7 @@
         <v>32</v>
       </c>
       <c r="D5" t="str">
-        <f>_xlfn.CONCAT("cn.etetet.",B5,".",M5)</f>
+        <f t="shared" ref="D5:D7" si="3">_xlfn.CONCAT("cn.etetet.",B5,".",M5)</f>
         <v>cn.etetet.twsmap.ChapterConfigCategory</v>
       </c>
       <c r="E5" t="str">
@@ -1259,7 +1262,7 @@
         <v>34</v>
       </c>
       <c r="D6" t="str">
-        <f>_xlfn.CONCAT("cn.etetet.",B6,".",M6)</f>
+        <f t="shared" si="3"/>
         <v>cn.etetet.twsmap.GameLevelConfigCategory</v>
       </c>
       <c r="E6" t="str">
@@ -1279,6 +1282,36 @@
       <c r="M6" t="str">
         <f t="shared" si="2"/>
         <v>GameLevelConfigCategory</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" spans="2:13">
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" t="str">
+        <f t="shared" si="3"/>
+        <v>cn.etetet.twsmap.EnergyBlockConfigCategory</v>
+      </c>
+      <c r="E7" t="str">
+        <f t="shared" si="0"/>
+        <v>EnergyBlockConfig</v>
+      </c>
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" t="str">
+        <f t="shared" si="1"/>
+        <v>..\..\..\..\cn.etetet.twsmap\Luban\Config\Datas\EnergyBlock.xlsx</v>
+      </c>
+      <c r="J7" t="s">
+        <v>33</v>
+      </c>
+      <c r="M7" t="str">
+        <f t="shared" si="2"/>
+        <v>EnergyBlockConfigCategory</v>
       </c>
     </row>
   </sheetData>
